--- a/product_selector_out/STM32WBA2x.xlsx
+++ b/product_selector_out/STM32WBA2x.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3348,9 +3348,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3573,14 +3573,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -3663,9 +3663,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3690,9 +3690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3915,14 +3915,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -4005,9 +4005,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4032,9 +4032,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4257,14 +4257,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -4347,9 +4347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4417,73 +4417,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32WBA23KE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32WBA25HE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WBA23CE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WBA2x.xlsx
+++ b/product_selector_out/STM32WBA2x.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
     </row>
@@ -3348,9 +3348,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3573,14 +3573,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -3663,9 +3663,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3690,9 +3690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3915,14 +3915,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -4005,9 +4005,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4032,9 +4032,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4257,14 +4257,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -4347,9 +4347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4421,6 +4421,72 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32WBA23KE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32WBA25HE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32WBA23CE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32WBA2x.xlsx
+++ b/product_selector_out/STM32WBA2x.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3348,9 +3348,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3573,14 +3573,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -3663,9 +3663,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3690,9 +3690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3915,14 +3915,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -4005,9 +4005,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4032,9 +4032,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4257,14 +4257,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -4347,9 +4347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4421,72 +4421,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32WBA23KE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32WBA25HE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WBA23CE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 34. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32WBA2x.xlsx
+++ b/product_selector_out/STM32WBA2x.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.1953125" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1350,6 +1357,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wba25ce.pdf</t>
         </is>
       </c>
@@ -1695,6 +1707,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2037,6 +2054,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2379,9 +2401,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2404,14 +2431,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -2429,6 +2455,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -2441,6 +2468,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -2467,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP15"/>
+  <dimension ref="A1:BQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2538,6 +2566,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2886,6 +2915,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2984,6 +3018,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3321,7 +3356,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3668,6 +3708,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4010,6 +4055,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4352,11 +4402,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
